--- a/data/trans_orig/P37C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023</t>
+          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23672</t>
+          <t>22787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67626</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105261</t>
+          <t>105924</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>52675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>76920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130837</t>
+          <t>131599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173204</t>
+          <t>174109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376077</t>
+          <t>374808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414583</t>
+          <t>414691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360754</t>
+          <t>359983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>385513</t>
+          <t>385221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>746484</t>
+          <t>742634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>790628</t>
+          <t>789510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26087</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40628</t>
+          <t>41440</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65430</t>
+          <t>66353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96092</t>
+          <t>97246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>63588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88049</t>
+          <t>89932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136512</t>
+          <t>136904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178173</t>
+          <t>180191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>332889</t>
+          <t>331808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366739</t>
+          <t>367298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274134</t>
+          <t>274603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303089</t>
+          <t>302928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>617303</t>
+          <t>613137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>662400</t>
+          <t>660048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15315</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15350</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39975</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30423</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149782</t>
+          <t>149058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>27276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43852</t>
+          <t>43961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>54302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>183801</t>
+          <t>184268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>467652</t>
+          <t>468131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>624457</t>
+          <t>620045</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113888</t>
+          <t>113562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132163</t>
+          <t>132620</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>593842</t>
+          <t>591678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>768910</t>
+          <t>763752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,49 +2904,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>11038</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3503</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>10215</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64968</t>
+          <t>65157</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>216727</t>
+          <t>219592</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>276056</t>
+          <t>279769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73699</t>
+          <t>75883</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>193534</t>
+          <t>190085</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>271651</t>
+          <t>258042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>451020</t>
+          <t>448525</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>712219</t>
+          <t>713713</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777147</t>
+          <t>774439</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>752004</t>
+          <t>755523</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>891991</t>
+          <t>886042</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1484040</t>
+          <t>1485822</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1686935</t>
+          <t>1694348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>425</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>824</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42093</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>33424</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70326</t>
+          <t>70740</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>86825</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>125770</t>
+          <t>127324</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,47 +3812,47 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>155094</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>115211</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>182594</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>18,55%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>155094</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>109719</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>181272</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>216276</t>
+          <t>215200</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>296605</t>
+          <t>296693</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>306392</t>
+          <t>303649</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>346881</t>
+          <t>346027</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>622071</t>
+          <t>621181</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>704105</t>
+          <t>698319</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>939800</t>
+          <t>938424</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1033621</t>
+          <t>1032838</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>26159</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>16406</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>41142</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>24374</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54931</t>
+          <t>57596</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>41485</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>85611</t>
+          <t>86976</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>142637</t>
+          <t>144841</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>184308</t>
+          <t>185801</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>200521</t>
+          <t>200912</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>259268</t>
+          <t>261049</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>131792</t>
+          <t>130205</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>179173</t>
+          <t>178673</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>536964</t>
+          <t>538414</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>582875</t>
+          <t>581950</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>682969</t>
+          <t>677071</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>744036</t>
+          <t>745422</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>14030</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>30812</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>55908</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>94792</t>
+          <t>94535</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>152004</t>
+          <t>154791</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>69036</t>
+          <t>67440</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>108666</t>
+          <t>107594</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>180122</t>
+          <t>179661</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>249344</t>
+          <t>249982</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>489593</t>
+          <t>520078</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>745916</t>
+          <t>747880</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>527376</t>
+          <t>522868</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>704388</t>
+          <t>704752</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1127454</t>
+          <t>1132311</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1423760</t>
+          <t>1415435</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2429165</t>
+          <t>2426416</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2757185</t>
+          <t>2707065</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2733735</t>
+          <t>2733716</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2939649</t>
+          <t>2945373</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5194811</t>
+          <t>5201838</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5537306</t>
+          <t>5537052</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -951,92 +951,92 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>14158</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7841</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23587</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6712</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12220</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>20869</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>13707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7740</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22787</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5873</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10932</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>19580</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>12556</t>
-        </is>
-      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86422</t>
+          <t>96230</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69182</t>
+          <t>79156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105924</t>
+          <t>116499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64293</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52675</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76920</t>
+          <t>85482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>150714</t>
+          <t>167852</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131599</t>
+          <t>145724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174109</t>
+          <t>192975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>395146</t>
+          <t>429496</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374808</t>
+          <t>408457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414691</t>
+          <t>448257</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>373816</t>
+          <t>406258</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359983</t>
+          <t>390920</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>385221</t>
+          <t>419897</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>768962</t>
+          <t>835753</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742634</t>
+          <t>811179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789510</t>
+          <t>860183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>503315</t>
+          <t>548763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>503315</t>
+          <t>548763</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>503315</t>
+          <t>548763</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>950782</t>
+          <t>1037173</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>950782</t>
+          <t>1037173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>950782</t>
+          <t>1037173</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27827</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>23311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>28731</t>
+          <t>32046</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41440</t>
+          <t>44865</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80273</t>
+          <t>88795</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66353</t>
+          <t>71995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97246</t>
+          <t>106077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>84844</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63588</t>
+          <t>71979</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89932</t>
+          <t>101569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>155955</t>
+          <t>173639</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136904</t>
+          <t>149554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180191</t>
+          <t>194004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>350165</t>
+          <t>370445</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331808</t>
+          <t>352618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367298</t>
+          <t>388005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>289484</t>
+          <t>318493</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274603</t>
+          <t>301956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>302928</t>
+          <t>333568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>639649</t>
+          <t>688937</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613137</t>
+          <t>667310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>660048</t>
+          <t>715993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>450492</t>
+          <t>481109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>450492</t>
+          <t>481109</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>450492</t>
+          <t>481109</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382420</t>
+          <t>422608</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382420</t>
+          <t>422608</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382420</t>
+          <t>422608</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>832912</t>
+          <t>903717</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>832912</t>
+          <t>903717</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>832912</t>
+          <t>903717</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>646</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>34356</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>37153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>102449</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>86254</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149058</t>
+          <t>122471</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27276</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>49340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>124902</t>
+          <t>142396</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54302</t>
+          <t>123450</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184268</t>
+          <t>164630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>545211</t>
+          <t>331365</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>468131</t>
+          <t>311006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>620045</t>
+          <t>349929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>124176</t>
+          <t>139186</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113562</t>
+          <t>129217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132620</t>
+          <t>149350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>669387</t>
+          <t>470551</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>591678</t>
+          <t>448887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>763752</t>
+          <t>491992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>665373</t>
+          <t>468533</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>665373</t>
+          <t>468533</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>665373</t>
+          <t>468533</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166295</t>
+          <t>186905</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166295</t>
+          <t>186905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166295</t>
+          <t>186905</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>831668</t>
+          <t>655438</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>831668</t>
+          <t>655438</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>831668</t>
+          <t>655438</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,42 +2831,42 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>7172</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5525</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,01%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>37550</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>61401</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34080</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65157</t>
+          <t>80029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>245020</t>
+          <t>275859</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>219592</t>
+          <t>249462</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>279769</t>
+          <t>311685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>146388</t>
+          <t>161417</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75883</t>
+          <t>142023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>190085</t>
+          <t>183110</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>391408</t>
+          <t>437276</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>258042</t>
+          <t>402823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>448525</t>
+          <t>478018</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>745659</t>
+          <t>803619</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>713713</t>
+          <t>765755</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774439</t>
+          <t>832250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>805383</t>
+          <t>668031</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>755523</t>
+          <t>645979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>886042</t>
+          <t>687148</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1551042</t>
+          <t>1471650</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1485822</t>
+          <t>1432458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1694348</t>
+          <t>1509569</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1027898</t>
+          <t>1124143</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1027898</t>
+          <t>1124143</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1027898</t>
+          <t>1124143</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>975300</t>
+          <t>858383</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>975300</t>
+          <t>858383</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>975300</t>
+          <t>858383</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2003198</t>
+          <t>1982526</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2003198</t>
+          <t>1982526</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2003198</t>
+          <t>1982526</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>61753</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15849</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33424</t>
+          <t>36331</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>54735</t>
+          <t>73358</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>42272</t>
+          <t>57614</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70740</t>
+          <t>91374</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -3792,17 +3792,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>105909</t>
+          <t>125453</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86825</t>
+          <t>104882</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>127324</t>
+          <t>147323</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>155094</t>
+          <t>174733</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>115211</t>
+          <t>154562</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>182594</t>
+          <t>194114</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>261003</t>
+          <t>300185</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>215200</t>
+          <t>270781</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>296693</t>
+          <t>329664</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>326010</t>
+          <t>377832</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>303649</t>
+          <t>352909</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>346027</t>
+          <t>400899</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>651596</t>
+          <t>619077</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>621181</t>
+          <t>597619</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>698319</t>
+          <t>640883</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>977606</t>
+          <t>996909</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>938424</t>
+          <t>965422</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>1029975</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>469327</t>
+          <t>555924</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>469327</t>
+          <t>555924</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>469327</t>
+          <t>555924</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>836138</t>
+          <t>827091</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>836138</t>
+          <t>827091</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>836138</t>
+          <t>827091</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1305465</t>
+          <t>1383015</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1305465</t>
+          <t>1383015</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1305465</t>
+          <t>1383015</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>10819</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>711</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,17 +4318,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>37629</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>46725</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>25506</t>
+          <t>32336</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>57596</t>
+          <t>70926</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>61853</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41485</t>
+          <t>44113</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>86976</t>
+          <t>85314</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>165660</t>
+          <t>185550</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>144841</t>
+          <t>163344</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>185801</t>
+          <t>209102</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>227512</t>
+          <t>248911</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>200912</t>
+          <t>220499</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>261049</t>
+          <t>281842</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>155789</t>
+          <t>145382</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>130205</t>
+          <t>123215</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>178673</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>560091</t>
+          <t>621638</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>538414</t>
+          <t>594851</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>581950</t>
+          <t>645576</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>715880</t>
+          <t>767021</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>677071</t>
+          <t>730376</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>745422</t>
+          <t>798139</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>231881</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>753835</t>
+          <t>838524</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>753835</t>
+          <t>838524</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>753835</t>
+          <t>838524</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>989172</t>
+          <t>1070406</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>989172</t>
+          <t>1070406</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>989172</t>
+          <t>1070406</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,17 +4887,17 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35074</t>
+          <t>34964</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -4930,59 +4930,59 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>36558</t>
+          <t>42069</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>17314</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10668</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>26245</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>16202</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>10494</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>25612</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>41643</t>
+          <t>47135</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>35690</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>55908</t>
+          <t>61648</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>126415</t>
+          <t>158726</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>94535</t>
+          <t>134580</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>154791</t>
+          <t>193084</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>102415</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>85273</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>122434</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>214993</t>
+          <t>261141</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>179661</t>
+          <t>229582</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>249982</t>
+          <t>297298</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>669577</t>
+          <t>752146</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>520078</t>
+          <t>701673</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>747880</t>
+          <t>809319</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>641918</t>
+          <t>718113</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>522868</t>
+          <t>679500</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>704752</t>
+          <t>757678</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1311495</t>
+          <t>1470259</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1132311</t>
+          <t>1401069</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1415435</t>
+          <t>1545711</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2517980</t>
+          <t>2458139</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2426416</t>
+          <t>2399110</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2707065</t>
+          <t>2512889</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2804546</t>
+          <t>2772682</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2733716</t>
+          <t>2728517</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2945373</t>
+          <t>2812967</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>5322526</t>
+          <t>5230821</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5201838</t>
+          <t>5150207</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5537052</t>
+          <t>5307676</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3351743</t>
+          <t>3410353</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3351743</t>
+          <t>3410353</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3351743</t>
+          <t>3410353</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3561455</t>
+          <t>3621922</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3561455</t>
+          <t>3621922</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3561455</t>
+          <t>3621922</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6913198</t>
+          <t>7032275</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6913198</t>
+          <t>7032275</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6913198</t>
+          <t>7032275</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
